--- a/Data Sheets/Entities.xlsx
+++ b/Data Sheets/Entities.xlsx
@@ -648,7 +648,7 @@
     <t>Engines, Diesel Engines</t>
   </si>
   <si>
-    <t>/Velocity +10, Noise = 0.0, FuelUsage = 0.0, EnergyUsage = -0.55, SmokeVisibility = 0.0, MaxGearChangeDelay = 7</t>
+    <t>/Velocity +10, Noise = 0.0, FuelUsage = 0.0, EnergyUsage = -1.0, SmokeVisibility = 0.0, MaxGearChangeDelay = 7</t>
   </si>
   <si>
     <t>Electric Engines</t>
@@ -657,7 +657,7 @@
     <t>Engines, Electric Engines</t>
   </si>
   <si>
-    <t>/Velocity +10, Noise = 0.0, FuelUsage = -10.0, EnergyUsage = 0.0, MaxGearChangeDelay = 7</t>
+    <t>/Velocity +10, Noise = 0.0, FuelUsage = -1.0, EnergyUsage = 0.0, MaxGearChangeDelay = 7</t>
   </si>
   <si>
     <t>Radio Room</t>

--- a/Data Sheets/Entities.xlsx
+++ b/Data Sheets/Entities.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="389">
   <si>
     <t>Displacement (t)</t>
   </si>
@@ -108,129 +108,120 @@
     <t>Recognized As</t>
   </si>
   <si>
-    <t>Type VIIC (Player)</t>
-  </si>
-  <si>
-    <t>Submarine</t>
+    <t>G7a Torpedo T1 - Pi1</t>
+  </si>
+  <si>
+    <t>Torpedo</t>
   </si>
   <si>
     <t>True</t>
   </si>
   <si>
-    <t>Observation Spot/SightRange = 8500, Observation Spot/GroupSightRange = 13, AreaSize = 7.5, SpawnSpacing = 300, HullFrontalVisibilityFactor *= 0.65, HullBaseVisibilityFactor *= 0.68, IndirectVisualDetectability *= 0.7, UnderwaterFadeFactor *= 2.0, CrushDepth = -8000</t>
+    <t>Range1 = 40000, Range2 = 40000, Range3 = 40000, Speed1 = 200, Speed2 = 150, Speed3 = 100, DudChance = 0.0, Damage = 50.0, CrewDamage = 0.9, DamageRadius = 35, DamageEffectsRadius = 7.0, DamageEffectsIntensity = 1.0, IndirectVisualDetectability *= 0.0, HullBaseVisibilityFactor *= 0.018, ArmDistance = 2.0, SonarDetectability *= 0.0, HomingSensitivity = 5000.0, EscortHomingSensitivity = 7500.0, MinPistolActivationAngle = 0, MaxPistolActivationAngle = 90, MagneticExplosionOnArm = 0.0, MagneticExplosionAfterArm = 0.0, MagneticExplosionFail = 0.0</t>
+  </si>
+  <si>
+    <t>Equipment/</t>
+  </si>
+  <si>
+    <t>G7a Torpedo T1 - Pi1.1</t>
+  </si>
+  <si>
+    <t>G7a Torpedo T1 - Pi3</t>
+  </si>
+  <si>
+    <t>G7a Torpedo T1 - Pi3 - FAT</t>
+  </si>
+  <si>
+    <t>G7a Torpedo T1 - Pi3 - LUT</t>
+  </si>
+  <si>
+    <t>G7e Torpedo T2 - Pi1</t>
+  </si>
+  <si>
+    <t>G7e Torpedo T2 - Pi1.1</t>
+  </si>
+  <si>
+    <t>G7e Torpedo T3 - Pi2</t>
+  </si>
+  <si>
+    <t>G7e Torpedo T3 - Pi2 - FAT</t>
+  </si>
+  <si>
+    <t>G7e Torpedo T3 - Pi2 - LUT</t>
+  </si>
+  <si>
+    <t>G7e Torpedo T3 - Pi2 - Prototype</t>
+  </si>
+  <si>
+    <t>G7es Zaunkönig Torpedo T5 - Pi4</t>
+  </si>
+  <si>
+    <t>G7es Zaunkönig Torpedo T5 - Pi4 - Prototype</t>
+  </si>
+  <si>
+    <t>G7a Torpedo T1 - Pi1 (Warmed)</t>
+  </si>
+  <si>
+    <t>Equipment/G7a Torpedo (T1)</t>
+  </si>
+  <si>
+    <t>G7a Torpedo T1 - Pi1.1 (Warmed)</t>
+  </si>
+  <si>
+    <t>G7a Torpedo T1 - Pi3 (Warmed)</t>
+  </si>
+  <si>
+    <t>G7a Torpedo T1 - Pi3 - FAT (Warmed)</t>
+  </si>
+  <si>
+    <t>G7a Torpedo T1 - Pi3 - LUT (Warmed)</t>
+  </si>
+  <si>
+    <t>G7e Torpedo T2 - Pi1 (Warmed)</t>
+  </si>
+  <si>
+    <t>Equipment/G7e Torpedo (T2)</t>
+  </si>
+  <si>
+    <t>G7e Torpedo T2 - Pi1.1 (Warmed)</t>
+  </si>
+  <si>
+    <t>G7e Torpedo T3 - Pi2 (Warmed)</t>
+  </si>
+  <si>
+    <t>Equipment/G7e Torpedo (T3)</t>
+  </si>
+  <si>
+    <t>G7e Torpedo T3 - Pi2 - FAT (Warmed)</t>
+  </si>
+  <si>
+    <t>G7e Torpedo T3 - Pi2 - LUT (Warmed)</t>
+  </si>
+  <si>
+    <t>G7e Torpedo T3 - Pi2 - Prototype (Warmed)</t>
+  </si>
+  <si>
+    <t>G7es Zaunkönig Torpedo T5 - Pi4 (Warmed)</t>
+  </si>
+  <si>
+    <t>Equipment/G7es "Zaunkönig" Torpedo (T5)</t>
+  </si>
+  <si>
+    <t>G7es Zaunkönig Torpedo T5 - Pi4 - Prototype (Warmed)</t>
+  </si>
+  <si>
+    <t>Sonar Decoy</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>Duration = 1300, CloakFactor = 0.1, CloakRadius = 2500, Noise = 0.75, TargetDepth = -20.0, MaintainDepthForce = 1000.0</t>
   </si>
   <si>
     <t>Entities/</t>
   </si>
   <si>
-    <t>G7a Torpedo T1 - Pi1</t>
-  </si>
-  <si>
-    <t>Torpedo</t>
-  </si>
-  <si>
-    <t>Range1 = 40000, Range2 = 40000, Range3 = 40000, Speed1 = 200, Speed2 = 150, Speed3 = 100, DudChance = 0.0, Damage = 50.0, CrewDamage = 0.9, DamageRadius = 35, DamageEffectsRadius = 7.0, DamageEffectsIntensity = 1.0, IndirectVisualDetectability *= 0.0, HullBaseVisibilityFactor *= 0.018, ArmDistance = 2.0, SonarDetectability *= 0.0, HomingSensitivity = 5000.0, EscortHomingSensitivity = 7500.0, MinPistolActivationAngle = 0, MaxPistolActivationAngle = 90, MagneticExplosionOnArm = 0.0, MagneticExplosionAfterArm = 0.0, MagneticExplosionFail = 0.0</t>
-  </si>
-  <si>
-    <t>Equipment/</t>
-  </si>
-  <si>
-    <t>G7a Torpedo T1 - Pi1.1</t>
-  </si>
-  <si>
-    <t>G7a Torpedo T1 - Pi3</t>
-  </si>
-  <si>
-    <t>G7a Torpedo T1 - Pi3 - FAT</t>
-  </si>
-  <si>
-    <t>G7a Torpedo T1 - Pi3 - LUT</t>
-  </si>
-  <si>
-    <t>G7e Torpedo T2 - Pi1</t>
-  </si>
-  <si>
-    <t>G7e Torpedo T2 - Pi1.1</t>
-  </si>
-  <si>
-    <t>G7e Torpedo T3 - Pi2</t>
-  </si>
-  <si>
-    <t>G7e Torpedo T3 - Pi2 - FAT</t>
-  </si>
-  <si>
-    <t>G7e Torpedo T3 - Pi2 - LUT</t>
-  </si>
-  <si>
-    <t>G7e Torpedo T3 - Pi2 - Prototype</t>
-  </si>
-  <si>
-    <t>G7es Zaunkönig Torpedo T5 - Pi4</t>
-  </si>
-  <si>
-    <t>G7es Zaunkönig Torpedo T5 - Pi4 - Prototype</t>
-  </si>
-  <si>
-    <t>G7a Torpedo T1 - Pi1 (Warmed)</t>
-  </si>
-  <si>
-    <t>Equipment/G7a Torpedo (T1)</t>
-  </si>
-  <si>
-    <t>G7a Torpedo T1 - Pi1.1 (Warmed)</t>
-  </si>
-  <si>
-    <t>G7a Torpedo T1 - Pi3 (Warmed)</t>
-  </si>
-  <si>
-    <t>G7a Torpedo T1 - Pi3 - FAT (Warmed)</t>
-  </si>
-  <si>
-    <t>G7a Torpedo T1 - Pi3 - LUT (Warmed)</t>
-  </si>
-  <si>
-    <t>G7e Torpedo T2 - Pi1 (Warmed)</t>
-  </si>
-  <si>
-    <t>Equipment/G7e Torpedo (T2)</t>
-  </si>
-  <si>
-    <t>G7e Torpedo T2 - Pi1.1 (Warmed)</t>
-  </si>
-  <si>
-    <t>G7e Torpedo T3 - Pi2 (Warmed)</t>
-  </si>
-  <si>
-    <t>Equipment/G7e Torpedo (T3)</t>
-  </si>
-  <si>
-    <t>G7e Torpedo T3 - Pi2 - FAT (Warmed)</t>
-  </si>
-  <si>
-    <t>G7e Torpedo T3 - Pi2 - LUT (Warmed)</t>
-  </si>
-  <si>
-    <t>G7e Torpedo T3 - Pi2 - Prototype (Warmed)</t>
-  </si>
-  <si>
-    <t>G7es Zaunkönig Torpedo T5 - Pi4 (Warmed)</t>
-  </si>
-  <si>
-    <t>Equipment/G7es "Zaunkönig" Torpedo (T5)</t>
-  </si>
-  <si>
-    <t>G7es Zaunkönig Torpedo T5 - Pi4 - Prototype (Warmed)</t>
-  </si>
-  <si>
-    <t>Sonar Decoy</t>
-  </si>
-  <si>
-    <t>False</t>
-  </si>
-  <si>
-    <t>Duration = 1300, CloakFactor = 0.1, CloakRadius = 2500, Noise = 0.75, TargetDepth = -20.0, MaintainDepthForce = 1000.0</t>
-  </si>
-  <si>
     <t>Tags</t>
   </si>
   <si>
@@ -585,7 +576,7 @@
     <t>Compressor, Diesel Compressor</t>
   </si>
   <si>
-    <t>FuelUsage = 0.0, OxygenCompression = 800, Noise = 0.0, OxygenUsage = 0.0</t>
+    <t>FuelUsage = 0.0, OxygenCompression = 40, Noise = 0.0, OxygenUsage = 0.0</t>
   </si>
   <si>
     <t>Electric Compressor</t>
@@ -1794,7 +1785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1" style="12"/>
@@ -1889,7 +1880,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="55.35" customHeight="1">
       <c r="A3" s="15" t="s">
         <v>22</v>
       </c>
@@ -1897,35 +1888,35 @@
         <v>23</v>
       </c>
       <c r="C3" s="15">
-        <v>133.7</v>
+        <v>200</v>
       </c>
       <c r="D3" s="15">
-        <v>769</v>
+        <v>0</v>
       </c>
       <c r="E3" s="15">
-        <v>871</v>
+        <v>0</v>
       </c>
       <c r="F3" s="15">
-        <v>67.1</v>
+        <v>7.16</v>
       </c>
       <c r="G3" s="15">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="H3" s="15">
-        <v>4.74</v>
-      </c>
-      <c r="I3" s="17">
-        <v>5.5</v>
+        <v>0</v>
+      </c>
+      <c r="I3" s="15">
+        <v>0</v>
       </c>
       <c r="J3" s="18"/>
       <c r="K3" s="15">
-        <v>15700</v>
+        <v>40</v>
       </c>
       <c r="L3" s="15">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M3" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N3" s="15" t="s">
         <v>24</v>
@@ -1934,18 +1925,18 @@
         <v>24</v>
       </c>
       <c r="P3" s="12">
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="15">
         <v>0</v>
       </c>
       <c r="R3" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="T3" s="16" t="s">
+      <c r="T3" s="19" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1954,7 +1945,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C4" s="15">
         <v>200</v>
@@ -2003,18 +1994,18 @@
         <v>1</v>
       </c>
       <c r="S4" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T4" s="19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" ht="55.35" customHeight="1">
       <c r="A5" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C5" s="15">
         <v>200</v>
@@ -2063,18 +2054,18 @@
         <v>1</v>
       </c>
       <c r="S5" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T5" s="19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" ht="55.35" customHeight="1">
       <c r="A6" s="15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C6" s="15">
         <v>200</v>
@@ -2123,18 +2114,18 @@
         <v>1</v>
       </c>
       <c r="S6" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T6" s="19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="55.35" customHeight="1">
       <c r="A7" s="15" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C7" s="15">
         <v>200</v>
@@ -2183,18 +2174,18 @@
         <v>1</v>
       </c>
       <c r="S7" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T7" s="19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" ht="55.35" customHeight="1">
       <c r="A8" s="15" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C8" s="15">
         <v>200</v>
@@ -2243,18 +2234,18 @@
         <v>1</v>
       </c>
       <c r="S8" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T8" s="19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" ht="55.35" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C9" s="15">
         <v>200</v>
@@ -2303,18 +2294,18 @@
         <v>1</v>
       </c>
       <c r="S9" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T9" s="19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" ht="55.35" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C10" s="15">
         <v>200</v>
@@ -2363,18 +2354,18 @@
         <v>1</v>
       </c>
       <c r="S10" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T10" s="19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" ht="55.35" customHeight="1">
       <c r="A11" s="15" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C11" s="15">
         <v>200</v>
@@ -2423,18 +2414,18 @@
         <v>1</v>
       </c>
       <c r="S11" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T11" s="19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" ht="55.35" customHeight="1">
       <c r="A12" s="15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C12" s="15">
         <v>200</v>
@@ -2483,18 +2474,18 @@
         <v>1</v>
       </c>
       <c r="S12" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T12" s="19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" ht="55.35" customHeight="1">
       <c r="A13" s="15" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C13" s="15">
         <v>200</v>
@@ -2543,18 +2534,18 @@
         <v>1</v>
       </c>
       <c r="S13" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T13" s="19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" ht="55.35" customHeight="1">
       <c r="A14" s="15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C14" s="15">
         <v>200</v>
@@ -2603,18 +2594,18 @@
         <v>1</v>
       </c>
       <c r="S14" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T14" s="19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" ht="55.35" customHeight="1">
       <c r="A15" s="15" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C15" s="15">
         <v>200</v>
@@ -2663,18 +2654,18 @@
         <v>1</v>
       </c>
       <c r="S15" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T15" s="19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" ht="55.35" customHeight="1">
       <c r="A16" s="15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C16" s="15">
         <v>200</v>
@@ -2723,18 +2714,18 @@
         <v>1</v>
       </c>
       <c r="S16" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T16" s="19" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" ht="55.35" customHeight="1">
       <c r="A17" s="15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C17" s="15">
         <v>200</v>
@@ -2783,18 +2774,18 @@
         <v>1</v>
       </c>
       <c r="S17" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T17" s="19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" ht="55.35" customHeight="1">
       <c r="A18" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C18" s="15">
         <v>200</v>
@@ -2843,18 +2834,18 @@
         <v>1</v>
       </c>
       <c r="S18" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T18" s="19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" ht="55.35" customHeight="1">
       <c r="A19" s="15" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C19" s="15">
         <v>200</v>
@@ -2903,18 +2894,18 @@
         <v>1</v>
       </c>
       <c r="S19" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T19" s="19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" ht="55.35" customHeight="1">
       <c r="A20" s="15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C20" s="15">
         <v>200</v>
@@ -2963,18 +2954,18 @@
         <v>1</v>
       </c>
       <c r="S20" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T20" s="19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" ht="55.35" customHeight="1">
       <c r="A21" s="15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C21" s="15">
         <v>200</v>
@@ -3023,18 +3014,18 @@
         <v>1</v>
       </c>
       <c r="S21" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T21" s="19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" ht="55.35" customHeight="1">
       <c r="A22" s="15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C22" s="15">
         <v>200</v>
@@ -3083,18 +3074,18 @@
         <v>1</v>
       </c>
       <c r="S22" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T22" s="19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" ht="55.35" customHeight="1">
       <c r="A23" s="15" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C23" s="15">
         <v>200</v>
@@ -3143,18 +3134,18 @@
         <v>1</v>
       </c>
       <c r="S23" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T23" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" ht="55.35" customHeight="1">
       <c r="A24" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C24" s="15">
         <v>200</v>
@@ -3203,18 +3194,18 @@
         <v>1</v>
       </c>
       <c r="S24" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T24" s="19" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" ht="55.35" customHeight="1">
       <c r="A25" s="15" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C25" s="15">
         <v>200</v>
@@ -3263,18 +3254,18 @@
         <v>1</v>
       </c>
       <c r="S25" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T25" s="19" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" ht="55.35" customHeight="1">
       <c r="A26" s="15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C26" s="15">
         <v>200</v>
@@ -3323,18 +3314,18 @@
         <v>1</v>
       </c>
       <c r="S26" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T26" s="19" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" ht="55.35" customHeight="1">
       <c r="A27" s="15" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C27" s="15">
         <v>200</v>
@@ -3383,18 +3374,18 @@
         <v>1</v>
       </c>
       <c r="S27" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T27" s="19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" ht="55.35" customHeight="1">
       <c r="A28" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C28" s="15">
         <v>200</v>
@@ -3443,132 +3434,73 @@
         <v>1</v>
       </c>
       <c r="S28" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T28" s="19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="17">
+        <v>0</v>
+      </c>
+      <c r="D29" s="17">
+        <v>0</v>
+      </c>
+      <c r="E29" s="17">
+        <v>0</v>
+      </c>
+      <c r="F29" s="17">
+        <v>0</v>
+      </c>
+      <c r="G29" s="17">
+        <v>0</v>
+      </c>
+      <c r="H29" s="17">
+        <v>0</v>
+      </c>
+      <c r="I29" s="17">
+        <v>0</v>
+      </c>
+      <c r="J29" s="18"/>
+      <c r="K29" s="17">
+        <v>0</v>
+      </c>
+      <c r="L29" s="20">
+        <v>100</v>
+      </c>
+      <c r="M29" s="20">
+        <v>1</v>
+      </c>
+      <c r="N29" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="O29" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="P29" s="12">
+        <v>120000</v>
+      </c>
+      <c r="Q29" s="20">
+        <v>0</v>
+      </c>
+      <c r="R29" s="16">
+        <v>0</v>
+      </c>
+      <c r="S29" s="16" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="29" ht="55.35" customHeight="1">
-      <c r="A29" s="15" t="s">
+      <c r="T29" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="15">
-        <v>200</v>
-      </c>
-      <c r="D29" s="15">
-        <v>0</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
-      </c>
-      <c r="F29" s="15">
-        <v>7.16</v>
-      </c>
-      <c r="G29" s="15">
-        <v>0</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0</v>
-      </c>
-      <c r="I29" s="15">
-        <v>0</v>
-      </c>
-      <c r="J29" s="18"/>
-      <c r="K29" s="15">
-        <v>40</v>
-      </c>
-      <c r="L29" s="15">
-        <v>0</v>
-      </c>
-      <c r="M29" s="15">
-        <v>0</v>
-      </c>
-      <c r="N29" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O29" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="P29" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="15">
-        <v>0</v>
-      </c>
-      <c r="R29" s="15">
-        <v>1</v>
-      </c>
-      <c r="S29" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="T29" s="19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="17">
-        <v>0</v>
-      </c>
-      <c r="D30" s="17">
-        <v>0</v>
-      </c>
-      <c r="E30" s="17">
-        <v>0</v>
-      </c>
-      <c r="F30" s="17">
-        <v>0</v>
-      </c>
-      <c r="G30" s="17">
-        <v>0</v>
-      </c>
-      <c r="H30" s="17">
-        <v>0</v>
-      </c>
-      <c r="I30" s="17">
-        <v>0</v>
-      </c>
-      <c r="J30" s="18"/>
-      <c r="K30" s="17">
-        <v>0</v>
-      </c>
-      <c r="L30" s="20">
-        <v>100</v>
-      </c>
-      <c r="M30" s="20">
-        <v>1</v>
-      </c>
-      <c r="N30" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="O30" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="P30" s="12">
-        <v>120000</v>
-      </c>
-      <c r="Q30" s="20">
-        <v>0</v>
-      </c>
-      <c r="R30" s="16">
-        <v>0</v>
-      </c>
-      <c r="S30" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="T30" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
+    </row>
+    <row r="30" ht="30" customHeight="1"/>
     <row r="31" ht="30" customHeight="1"/>
     <row r="32" ht="30" customHeight="1"/>
     <row r="33" ht="30" customHeight="1"/>
@@ -3583,7 +3515,6 @@
     <row r="42" ht="30" customHeight="1"/>
     <row r="43" ht="30" customHeight="1"/>
     <row r="44" ht="30" customHeight="1"/>
-    <row r="45" ht="30" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3601,66 +3532,66 @@
         <v>1</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="N1" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="O1" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="M1" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="P1" s="11" t="s">
         <v>19</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C2" s="11">
         <v>4000</v>
@@ -3702,18 +3633,18 @@
         <v>40</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C3" s="11">
         <v>4000</v>
@@ -3755,18 +3686,18 @@
         <v>40</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C4" s="11">
         <v>4000</v>
@@ -3808,18 +3739,18 @@
         <v>40</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C5" s="11">
         <v>8000</v>
@@ -3861,18 +3792,18 @@
         <v>40</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C6" s="11">
         <v>12000</v>
@@ -3914,18 +3845,18 @@
         <v>40</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C7" s="11">
         <v>4000</v>
@@ -3967,18 +3898,18 @@
         <v>40</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="Q7" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C8" s="11">
         <v>0</v>
@@ -4020,18 +3951,18 @@
         <v>40</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C9" s="11">
         <v>8000</v>
@@ -4073,18 +4004,18 @@
         <v>40</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q9" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C10" s="11">
         <v>24000</v>
@@ -4126,18 +4057,18 @@
         <v>40</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C11" s="11">
         <v>16000</v>
@@ -4179,18 +4110,18 @@
         <v>40</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q11" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C12" s="11">
         <v>0</v>
@@ -4232,18 +4163,18 @@
         <v>40</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="Q12" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C13" s="11">
         <v>3500</v>
@@ -4285,18 +4216,18 @@
         <v>40</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="Q13" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C14" s="11">
         <v>7000</v>
@@ -4338,18 +4269,18 @@
         <v>40</v>
       </c>
       <c r="P14" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q14" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C15" s="11">
         <v>14000</v>
@@ -4391,18 +4322,18 @@
         <v>40</v>
       </c>
       <c r="P15" s="11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q15" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C16" s="11">
         <v>21000</v>
@@ -4444,18 +4375,18 @@
         <v>40</v>
       </c>
       <c r="P16" s="11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q16" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C17" s="11">
         <v>6000</v>
@@ -4497,18 +4428,18 @@
         <v>40</v>
       </c>
       <c r="P17" s="11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Q17" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C18" s="11">
         <v>4000</v>
@@ -4550,18 +4481,18 @@
         <v>40</v>
       </c>
       <c r="P18" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C19" s="11">
         <v>8000</v>
@@ -4603,18 +4534,18 @@
         <v>40</v>
       </c>
       <c r="P19" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C20" s="11">
         <v>16000</v>
@@ -4656,18 +4587,18 @@
         <v>40</v>
       </c>
       <c r="P20" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C21" s="11">
         <v>24000</v>
@@ -4709,18 +4640,18 @@
         <v>40</v>
       </c>
       <c r="P21" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Q21" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C22" s="11">
         <v>4000</v>
@@ -4762,15 +4693,15 @@
         <v>40</v>
       </c>
       <c r="Q22" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C23" s="11">
         <v>4000</v>
@@ -4812,15 +4743,15 @@
         <v>40</v>
       </c>
       <c r="Q23" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C24" s="11">
         <v>4000</v>
@@ -4862,15 +4793,15 @@
         <v>40</v>
       </c>
       <c r="Q24" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C25" s="11">
         <v>8000</v>
@@ -4912,18 +4843,18 @@
         <v>40</v>
       </c>
       <c r="P25" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="Q25" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C26" s="11">
         <v>4000</v>
@@ -4965,18 +4896,18 @@
         <v>40</v>
       </c>
       <c r="P26" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C27" s="11">
         <v>0</v>
@@ -5018,18 +4949,18 @@
         <v>1</v>
       </c>
       <c r="P27" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C28" s="11">
         <v>10000</v>
@@ -5071,18 +5002,18 @@
         <v>1</v>
       </c>
       <c r="P28" s="11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C29" s="11">
         <v>18000</v>
@@ -5124,18 +5055,18 @@
         <v>1</v>
       </c>
       <c r="P29" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q29" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C30" s="11">
         <v>30000</v>
@@ -5177,18 +5108,18 @@
         <v>1</v>
       </c>
       <c r="P30" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q30" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C31" s="11">
         <v>250</v>
@@ -5230,7 +5161,7 @@
         <v>40</v>
       </c>
       <c r="P31" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="Q31" s="11">
         <v>1</v>
@@ -5238,10 +5169,10 @@
     </row>
     <row r="32">
       <c r="A32" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C32" s="11">
         <v>9000</v>
@@ -5288,10 +5219,10 @@
     </row>
     <row r="33">
       <c r="A33" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C33" s="11">
         <v>3000</v>
@@ -5333,15 +5264,15 @@
         <v>4000</v>
       </c>
       <c r="Q33" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C34" s="11">
         <v>250</v>
@@ -5383,18 +5314,18 @@
         <v>1</v>
       </c>
       <c r="P34" s="11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q34" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C35" s="11">
         <v>2000</v>
@@ -5441,10 +5372,10 @@
     </row>
     <row r="36">
       <c r="A36" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C36" s="11">
         <v>2000</v>
@@ -5491,10 +5422,10 @@
     </row>
     <row r="37">
       <c r="A37" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C37" s="11">
         <v>750</v>
@@ -5536,7 +5467,7 @@
         <v>1</v>
       </c>
       <c r="P37" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="Q37" s="11">
         <v>3</v>
@@ -5544,10 +5475,10 @@
     </row>
     <row r="38">
       <c r="A38" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C38" s="11">
         <v>5000</v>
@@ -5594,10 +5525,10 @@
     </row>
     <row r="39">
       <c r="A39" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C39" s="11">
         <v>5000</v>
@@ -5644,10 +5575,10 @@
     </row>
     <row r="40">
       <c r="A40" s="11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C40" s="11">
         <v>200</v>
@@ -5689,7 +5620,7 @@
         <v>4</v>
       </c>
       <c r="P40" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q40" s="11">
         <v>1</v>
@@ -5697,10 +5628,10 @@
     </row>
     <row r="41">
       <c r="A41" s="11" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C41" s="11">
         <v>5000</v>
@@ -5742,15 +5673,15 @@
         <v>40</v>
       </c>
       <c r="Q41" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C42" s="11">
         <v>10000</v>
@@ -5792,15 +5723,15 @@
         <v>40</v>
       </c>
       <c r="Q42" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C43" s="11">
         <v>20000</v>
@@ -5842,15 +5773,15 @@
         <v>40</v>
       </c>
       <c r="Q43" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C44" s="11">
         <v>40000</v>
@@ -5892,15 +5823,15 @@
         <v>40</v>
       </c>
       <c r="Q44" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C45" s="11">
         <v>500</v>
@@ -5947,10 +5878,10 @@
     </row>
     <row r="46">
       <c r="A46" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C46" s="11">
         <v>500</v>
@@ -5997,10 +5928,10 @@
     </row>
     <row r="47">
       <c r="A47" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C47" s="11">
         <v>6000</v>
@@ -6047,10 +5978,10 @@
     </row>
     <row r="48">
       <c r="A48" s="11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C48" s="11">
         <v>6000</v>
@@ -6097,10 +6028,10 @@
     </row>
     <row r="49">
       <c r="A49" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C49" s="11">
         <v>3000</v>
@@ -6142,15 +6073,15 @@
         <v>400</v>
       </c>
       <c r="Q49" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C50" s="11">
         <v>1000</v>
@@ -6192,15 +6123,15 @@
         <v>5</v>
       </c>
       <c r="Q50" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C51" s="11">
         <v>0</v>
@@ -6242,18 +6173,18 @@
         <v>1</v>
       </c>
       <c r="P51" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q51" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C52" s="11">
         <v>0</v>
@@ -6295,18 +6226,18 @@
         <v>1</v>
       </c>
       <c r="P52" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q52" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C53" s="11">
         <v>0</v>
@@ -6348,18 +6279,18 @@
         <v>1</v>
       </c>
       <c r="P53" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q53" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C54" s="11">
         <v>0</v>
@@ -6401,18 +6332,18 @@
         <v>1</v>
       </c>
       <c r="P54" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q54" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C55" s="11">
         <v>0</v>
@@ -6454,18 +6385,18 @@
         <v>1</v>
       </c>
       <c r="P55" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q55" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C56" s="11">
         <v>0</v>
@@ -6507,18 +6438,18 @@
         <v>1</v>
       </c>
       <c r="P56" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q56" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C57" s="11">
         <v>0</v>
@@ -6560,18 +6491,18 @@
         <v>1</v>
       </c>
       <c r="P57" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q57" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C58" s="11">
         <v>0</v>
@@ -6613,18 +6544,18 @@
         <v>1</v>
       </c>
       <c r="P58" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q58" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C59" s="11">
         <v>0</v>
@@ -6666,18 +6597,18 @@
         <v>1</v>
       </c>
       <c r="P59" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q59" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C60" s="11">
         <v>0</v>
@@ -6719,18 +6650,18 @@
         <v>1</v>
       </c>
       <c r="P60" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q60" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C61" s="11">
         <v>0</v>
@@ -6772,18 +6703,18 @@
         <v>1</v>
       </c>
       <c r="P61" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q61" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C62" s="11">
         <v>0</v>
@@ -6825,18 +6756,18 @@
         <v>1</v>
       </c>
       <c r="P62" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q62" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C63" s="11">
         <v>0</v>
@@ -6878,18 +6809,18 @@
         <v>1</v>
       </c>
       <c r="P63" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q63" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C64" s="11">
         <v>0</v>
@@ -6931,18 +6862,18 @@
         <v>1</v>
       </c>
       <c r="P64" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q64" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C65" s="11">
         <v>0</v>
@@ -6984,18 +6915,18 @@
         <v>1</v>
       </c>
       <c r="P65" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q65" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C66" s="11">
         <v>0</v>
@@ -7037,18 +6968,18 @@
         <v>1</v>
       </c>
       <c r="P66" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q66" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C67" s="11">
         <v>0</v>
@@ -7090,18 +7021,18 @@
         <v>1</v>
       </c>
       <c r="P67" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q67" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C68" s="11">
         <v>0</v>
@@ -7143,18 +7074,18 @@
         <v>1</v>
       </c>
       <c r="P68" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q68" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C69" s="11">
         <v>0</v>
@@ -7196,18 +7127,18 @@
         <v>1</v>
       </c>
       <c r="P69" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q69" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C70" s="11">
         <v>0</v>
@@ -7249,18 +7180,18 @@
         <v>1</v>
       </c>
       <c r="P70" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q70" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C71" s="11">
         <v>0</v>
@@ -7302,18 +7233,18 @@
         <v>1</v>
       </c>
       <c r="P71" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q71" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C72" s="11">
         <v>0</v>
@@ -7355,18 +7286,18 @@
         <v>1</v>
       </c>
       <c r="P72" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q72" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C73" s="11">
         <v>0</v>
@@ -7408,18 +7339,18 @@
         <v>1</v>
       </c>
       <c r="P73" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q73" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C74" s="11">
         <v>0</v>
@@ -7461,18 +7392,18 @@
         <v>1</v>
       </c>
       <c r="P74" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q74" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C75" s="11">
         <v>0</v>
@@ -7514,18 +7445,18 @@
         <v>1</v>
       </c>
       <c r="P75" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q75" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C76" s="11">
         <v>0</v>
@@ -7567,18 +7498,18 @@
         <v>1</v>
       </c>
       <c r="P76" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q76" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C77" s="11">
         <v>0</v>
@@ -7620,18 +7551,18 @@
         <v>40</v>
       </c>
       <c r="P77" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q77" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C78" s="11">
         <v>0</v>
@@ -7673,18 +7604,18 @@
         <v>40</v>
       </c>
       <c r="P78" s="11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Q78" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C79" s="11">
         <v>5000</v>
@@ -7726,15 +7657,15 @@
         <v>40</v>
       </c>
       <c r="P79" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C80" s="11">
         <v>3000</v>
@@ -7776,15 +7707,15 @@
         <v>40</v>
       </c>
       <c r="P80" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C81" s="11">
         <v>0</v>
@@ -7826,15 +7757,15 @@
         <v>40</v>
       </c>
       <c r="P81" s="11" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C82" s="11">
         <v>0</v>
@@ -7876,15 +7807,15 @@
         <v>40</v>
       </c>
       <c r="P82" s="11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C83" s="11">
         <v>0</v>
@@ -7926,15 +7857,15 @@
         <v>40</v>
       </c>
       <c r="P83" s="11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C84" s="11">
         <v>0</v>
@@ -7976,12 +7907,12 @@
         <v>40</v>
       </c>
       <c r="P84" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C85" s="11">
         <v>0</v>
@@ -8023,12 +7954,12 @@
         <v>1</v>
       </c>
       <c r="P85" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C86" s="11">
         <v>0</v>
@@ -8070,12 +8001,12 @@
         <v>40</v>
       </c>
       <c r="P86" s="11" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C87" s="11">
         <v>0</v>
@@ -8117,15 +8048,15 @@
         <v>40</v>
       </c>
       <c r="P87" s="11" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C88" s="11">
         <v>0</v>
@@ -8167,15 +8098,15 @@
         <v>40</v>
       </c>
       <c r="P88" s="11" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C89" s="11">
         <v>0</v>
@@ -8217,12 +8148,12 @@
         <v>40</v>
       </c>
       <c r="P89" s="11" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C90" s="11">
         <v>0</v>
@@ -8264,15 +8195,15 @@
         <v>40</v>
       </c>
       <c r="P90" s="11" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C91" s="11">
         <v>0</v>
@@ -8316,10 +8247,10 @@
     </row>
     <row r="92">
       <c r="A92" s="11" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C92" s="11">
         <v>2000</v>
@@ -8361,15 +8292,15 @@
         <v>40</v>
       </c>
       <c r="P92" s="11" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C93" s="11">
         <v>0</v>
@@ -8411,15 +8342,15 @@
         <v>40</v>
       </c>
       <c r="P93" s="11" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C94" s="11">
         <v>0</v>
@@ -8461,15 +8392,15 @@
         <v>40</v>
       </c>
       <c r="P94" s="11" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C95" s="11">
         <v>0</v>
@@ -8511,15 +8442,15 @@
         <v>40</v>
       </c>
       <c r="P95" s="11" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C96" s="11">
         <v>0</v>
@@ -8563,10 +8494,10 @@
     </row>
     <row r="97">
       <c r="A97" s="11" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C97" s="11">
         <v>0</v>
@@ -8608,15 +8539,15 @@
         <v>40</v>
       </c>
       <c r="P97" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C98" s="11">
         <v>0</v>
@@ -8658,15 +8589,15 @@
         <v>40</v>
       </c>
       <c r="P98" s="11" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C99" s="11">
         <v>0</v>
@@ -8708,15 +8639,15 @@
         <v>40</v>
       </c>
       <c r="P99" s="11" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C100" s="11">
         <v>0</v>
@@ -8758,15 +8689,15 @@
         <v>40</v>
       </c>
       <c r="P100" s="11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C101" s="11">
         <v>0</v>
@@ -8808,15 +8739,15 @@
         <v>40</v>
       </c>
       <c r="P101" s="11" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C102" s="11">
         <v>0</v>
@@ -8858,15 +8789,15 @@
         <v>40</v>
       </c>
       <c r="P102" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C103" s="11">
         <v>0</v>
@@ -8908,15 +8839,15 @@
         <v>40</v>
       </c>
       <c r="P103" s="11" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="11" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C104" s="11">
         <v>0</v>
@@ -8958,15 +8889,15 @@
         <v>40</v>
       </c>
       <c r="P104" s="11" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C105" s="11">
         <v>0</v>
@@ -9008,15 +8939,15 @@
         <v>40</v>
       </c>
       <c r="P105" s="11" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C106" s="11">
         <v>0</v>
@@ -9058,15 +8989,15 @@
         <v>40</v>
       </c>
       <c r="P106" s="11" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C107" s="11">
         <v>0</v>
@@ -9108,15 +9039,15 @@
         <v>40</v>
       </c>
       <c r="P107" s="11" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C108" s="11">
         <v>0</v>
@@ -9158,15 +9089,15 @@
         <v>40</v>
       </c>
       <c r="P108" s="11" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="11" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C109" s="11">
         <v>0</v>
@@ -9208,15 +9139,15 @@
         <v>40</v>
       </c>
       <c r="P109" s="11" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C110" s="11">
         <v>0</v>
@@ -9258,18 +9189,18 @@
         <v>40</v>
       </c>
       <c r="P110" s="11" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D111" s="11">
         <v>14246</v>
@@ -9308,18 +9239,18 @@
         <v>4000</v>
       </c>
       <c r="P111" s="11" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="11" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D112" s="11">
         <v>14246</v>
@@ -9358,18 +9289,18 @@
         <v>4000</v>
       </c>
       <c r="P112" s="11" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D113" s="11">
         <v>14246</v>
@@ -9408,18 +9339,18 @@
         <v>4000</v>
       </c>
       <c r="P113" s="11" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D114" s="11">
         <v>14246</v>
@@ -9458,18 +9389,18 @@
         <v>4000</v>
       </c>
       <c r="P114" s="11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D115" s="11">
         <v>14246</v>
@@ -9508,18 +9439,18 @@
         <v>4000</v>
       </c>
       <c r="P115" s="11" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D116" s="11">
         <v>14246</v>
@@ -9558,18 +9489,18 @@
         <v>4000</v>
       </c>
       <c r="P116" s="11" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D117" s="11">
         <v>14246</v>
@@ -9608,18 +9539,18 @@
         <v>4000</v>
       </c>
       <c r="P117" s="11" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="11" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D118" s="11">
         <v>14246</v>
@@ -9658,18 +9589,18 @@
         <v>4000</v>
       </c>
       <c r="P118" s="11" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D119" s="11">
         <v>14246</v>
@@ -9708,18 +9639,18 @@
         <v>4000</v>
       </c>
       <c r="P119" s="11" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="11" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D120" s="11">
         <v>14246</v>
@@ -9758,15 +9689,15 @@
         <v>4000</v>
       </c>
       <c r="P120" s="11" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C121" s="11">
         <v>0</v>
@@ -9810,10 +9741,10 @@
     </row>
     <row r="122">
       <c r="A122" s="11" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C122" s="11">
         <v>0</v>
@@ -9855,65 +9786,65 @@
         <v>1</v>
       </c>
       <c r="P122" s="11" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B123" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="C123" s="11">
+        <v>0</v>
+      </c>
+      <c r="D123" s="11">
+        <v>14246</v>
+      </c>
+      <c r="E123" s="11">
+        <v>0</v>
+      </c>
+      <c r="F123" s="11">
+        <v>0</v>
+      </c>
+      <c r="G123" s="11">
+        <v>1</v>
+      </c>
+      <c r="H123" s="11">
+        <v>0</v>
+      </c>
+      <c r="I123" s="11">
+        <v>1</v>
+      </c>
+      <c r="J123" s="11">
+        <v>0</v>
+      </c>
+      <c r="K123" s="11">
+        <v>60</v>
+      </c>
+      <c r="L123" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M123" s="11">
+        <v>0</v>
+      </c>
+      <c r="N123" s="11">
+        <v>1</v>
+      </c>
+      <c r="O123" s="11">
+        <v>1</v>
+      </c>
+      <c r="P123" s="11" t="s">
         <v>283</v>
-      </c>
-      <c r="C123" s="11">
-        <v>0</v>
-      </c>
-      <c r="D123" s="11">
-        <v>14246</v>
-      </c>
-      <c r="E123" s="11">
-        <v>0</v>
-      </c>
-      <c r="F123" s="11">
-        <v>0</v>
-      </c>
-      <c r="G123" s="11">
-        <v>1</v>
-      </c>
-      <c r="H123" s="11">
-        <v>0</v>
-      </c>
-      <c r="I123" s="11">
-        <v>1</v>
-      </c>
-      <c r="J123" s="11">
-        <v>0</v>
-      </c>
-      <c r="K123" s="11">
-        <v>60</v>
-      </c>
-      <c r="L123" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M123" s="11">
-        <v>0</v>
-      </c>
-      <c r="N123" s="11">
-        <v>1</v>
-      </c>
-      <c r="O123" s="11">
-        <v>1</v>
-      </c>
-      <c r="P123" s="11" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C124" s="11">
         <v>0</v>
@@ -9955,15 +9886,15 @@
         <v>1</v>
       </c>
       <c r="P124" s="11" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C125" s="11">
         <v>0</v>
@@ -10005,15 +9936,15 @@
         <v>1</v>
       </c>
       <c r="P125" s="11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="11" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C126" s="11">
         <v>0</v>
@@ -10055,15 +9986,15 @@
         <v>1</v>
       </c>
       <c r="P126" s="11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C127" s="11">
         <v>0</v>
@@ -10105,15 +10036,15 @@
         <v>1</v>
       </c>
       <c r="P127" s="11" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C128" s="11">
         <v>0</v>
@@ -10155,15 +10086,15 @@
         <v>1</v>
       </c>
       <c r="P128" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C129" s="11">
         <v>0</v>
@@ -10205,15 +10136,15 @@
         <v>1</v>
       </c>
       <c r="P129" s="11" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C130" s="11">
         <v>0</v>
@@ -10255,15 +10186,15 @@
         <v>1</v>
       </c>
       <c r="P130" s="11" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="11" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C131" s="11">
         <v>0</v>
@@ -10305,15 +10236,15 @@
         <v>1</v>
       </c>
       <c r="P131" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="11" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C132" s="11">
         <v>0</v>
@@ -10355,15 +10286,15 @@
         <v>1</v>
       </c>
       <c r="P132" s="11" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="11" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C133" s="11">
         <v>0</v>
@@ -10405,15 +10336,15 @@
         <v>1</v>
       </c>
       <c r="P133" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C134" s="11">
         <v>0</v>
@@ -10455,12 +10386,12 @@
         <v>1</v>
       </c>
       <c r="P134" s="11" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="11" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C135" s="11">
         <v>0</v>
@@ -10502,12 +10433,12 @@
         <v>1</v>
       </c>
       <c r="P135" s="11" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="11" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C136" s="11">
         <v>0</v>
@@ -10549,12 +10480,12 @@
         <v>1</v>
       </c>
       <c r="P136" s="11" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C137" s="11">
         <v>0</v>
@@ -10596,12 +10527,12 @@
         <v>1</v>
       </c>
       <c r="P137" s="11" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="11" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C138" s="11">
         <v>0</v>
@@ -10643,12 +10574,12 @@
         <v>1</v>
       </c>
       <c r="P138" s="11" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="11" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C139" s="11">
         <v>0</v>
@@ -10690,12 +10621,12 @@
         <v>1</v>
       </c>
       <c r="P139" s="11" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C140" s="11">
         <v>0</v>
@@ -10737,15 +10668,15 @@
         <v>1</v>
       </c>
       <c r="P140" s="11" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="11" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C141" s="11">
         <v>0</v>
@@ -10787,15 +10718,15 @@
         <v>1</v>
       </c>
       <c r="Q141" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="11" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C142" s="11">
         <v>0</v>
@@ -10837,15 +10768,15 @@
         <v>1</v>
       </c>
       <c r="Q142" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="11" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C143" s="11">
         <v>0</v>
@@ -10887,18 +10818,18 @@
         <v>1</v>
       </c>
       <c r="P143" s="11" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="Q143" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="11" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C144" s="11">
         <v>0</v>
@@ -10940,18 +10871,18 @@
         <v>1</v>
       </c>
       <c r="P144" s="11" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="Q144" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="11" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C145" s="11">
         <v>0</v>
@@ -10993,15 +10924,15 @@
         <v>1</v>
       </c>
       <c r="P145" s="11" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="11" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C146" s="11">
         <v>0</v>
@@ -11043,15 +10974,15 @@
         <v>1</v>
       </c>
       <c r="R146" s="11" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C147" s="11">
         <v>0</v>
@@ -11093,15 +11024,15 @@
         <v>1</v>
       </c>
       <c r="P147" s="11" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="11" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C148" s="11">
         <v>1</v>
@@ -11143,15 +11074,15 @@
         <v>1</v>
       </c>
       <c r="P148" s="11" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="11" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B149" s="11" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C149" s="11">
         <v>2</v>
@@ -11193,15 +11124,15 @@
         <v>1</v>
       </c>
       <c r="P149" s="11" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="11" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C150" s="11">
         <v>0</v>
@@ -11245,7 +11176,7 @@
     </row>
     <row r="151">
       <c r="A151" s="11" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C151" s="11">
         <v>0</v>
@@ -11287,12 +11218,12 @@
         <v>1</v>
       </c>
       <c r="P151" s="11" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="11" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C152" s="11">
         <v>0</v>
@@ -11336,13 +11267,13 @@
     </row>
     <row r="153">
       <c r="A153" s="11" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D153" s="11">
         <v>14246</v>
@@ -11381,7 +11312,7 @@
         <v>40</v>
       </c>
       <c r="P153" s="11" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -11389,13 +11320,13 @@
     </row>
     <row r="154">
       <c r="A154" s="11" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D154" s="11">
         <v>14246</v>
@@ -11434,7 +11365,7 @@
         <v>40</v>
       </c>
       <c r="P154" s="11" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="Q154" s="10"/>
       <c r="R154" s="10"/>
@@ -11442,13 +11373,13 @@
     </row>
     <row r="155">
       <c r="A155" s="11" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D155" s="11">
         <v>14246</v>
@@ -11487,7 +11418,7 @@
         <v>40</v>
       </c>
       <c r="P155" s="11" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -11495,13 +11426,13 @@
     </row>
     <row r="156">
       <c r="A156" s="11" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D156" s="11">
         <v>14246</v>
@@ -11540,7 +11471,7 @@
         <v>40</v>
       </c>
       <c r="P156" s="11" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="Q156" s="9"/>
       <c r="R156" s="9"/>
@@ -11548,13 +11479,13 @@
     </row>
     <row r="157">
       <c r="A157" s="11" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D157" s="11">
         <v>14246</v>
@@ -11593,7 +11524,7 @@
         <v>40</v>
       </c>
       <c r="P157" s="11" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -11601,13 +11532,13 @@
     </row>
     <row r="158">
       <c r="A158" s="11" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D158" s="11">
         <v>14246</v>
@@ -11646,23 +11577,23 @@
         <v>40</v>
       </c>
       <c r="P158" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="Q158" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="R158" s="9"/>
       <c r="S158" s="9"/>
     </row>
     <row r="159">
       <c r="A159" s="11" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D159" s="11">
         <v>14246</v>
@@ -11701,23 +11632,23 @@
         <v>40</v>
       </c>
       <c r="P159" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="Q159" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="R159" s="9"/>
       <c r="S159" s="9"/>
     </row>
     <row r="160">
       <c r="A160" s="11" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D160" s="11">
         <v>14246</v>
@@ -11756,7 +11687,7 @@
         <v>40</v>
       </c>
       <c r="P160" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q160" s="9"/>
       <c r="R160" s="9"/>
@@ -11764,13 +11695,13 @@
     </row>
     <row r="161">
       <c r="A161" s="11" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D161" s="11">
         <v>14246</v>
@@ -11809,7 +11740,7 @@
         <v>40</v>
       </c>
       <c r="P161" s="11" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11817,13 +11748,13 @@
     </row>
     <row r="162">
       <c r="A162" s="11" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D162" s="11">
         <v>14246</v>
@@ -11862,7 +11793,7 @@
         <v>40</v>
       </c>
       <c r="P162" s="11" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="Q162" s="9"/>
       <c r="R162" s="9"/>
@@ -11870,13 +11801,13 @@
     </row>
     <row r="163">
       <c r="A163" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D163" s="11">
         <v>14246</v>
@@ -11915,16 +11846,16 @@
         <v>40</v>
       </c>
       <c r="Q163" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="11" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B164" s="10"/>
       <c r="C164" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D164" s="11">
         <v>14246</v>
@@ -11957,13 +11888,13 @@
         <v>0</v>
       </c>
       <c r="N164" s="11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O164" s="11" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="P164" s="11" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="Q164" s="10"/>
       <c r="R164" s="10"/>
@@ -11971,11 +11902,11 @@
     </row>
     <row r="165">
       <c r="A165" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B165" s="10"/>
       <c r="C165" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D165" s="11">
         <v>14246</v>
@@ -12008,13 +11939,13 @@
         <v>0</v>
       </c>
       <c r="N165" s="11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O165" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="P165" s="11" t="s">
         <v>360</v>
-      </c>
-      <c r="P165" s="11" t="s">
-        <v>363</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -12022,11 +11953,11 @@
     </row>
     <row r="166">
       <c r="A166" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B166" s="10"/>
       <c r="C166" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D166" s="10">
         <v>14246</v>
@@ -12065,7 +11996,7 @@
         <v>40</v>
       </c>
       <c r="P166" s="10" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="Q166" s="10"/>
       <c r="R166" s="10"/>
@@ -12073,11 +12004,11 @@
     </row>
     <row r="167">
       <c r="A167" s="10" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B167" s="10"/>
       <c r="C167" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D167" s="10">
         <v>14246</v>
@@ -12116,7 +12047,7 @@
         <v>40</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Q167" s="10"/>
       <c r="R167" s="10"/>
@@ -12124,11 +12055,11 @@
     </row>
     <row r="168">
       <c r="A168" s="10" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B168" s="10"/>
       <c r="C168" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D168" s="10">
         <v>14246</v>
@@ -12167,7 +12098,7 @@
         <v>40</v>
       </c>
       <c r="P168" s="10" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="Q168" s="10"/>
       <c r="R168" s="10"/>
@@ -12175,11 +12106,11 @@
     </row>
     <row r="169">
       <c r="A169" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B169" s="10"/>
       <c r="C169" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D169" s="10">
         <v>14246</v>
@@ -12218,7 +12149,7 @@
         <v>40</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -12226,11 +12157,11 @@
     </row>
     <row r="170">
       <c r="A170" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B170" s="10"/>
       <c r="C170" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D170" s="10">
         <v>14246</v>
@@ -12269,7 +12200,7 @@
         <v>40</v>
       </c>
       <c r="P170" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="Q170" s="10"/>
       <c r="R170" s="10"/>
@@ -12277,11 +12208,11 @@
     </row>
     <row r="171">
       <c r="A171" s="10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B171" s="10"/>
       <c r="C171" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D171" s="10">
         <v>14246</v>
@@ -12320,7 +12251,7 @@
         <v>40</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -12328,11 +12259,11 @@
     </row>
     <row r="172">
       <c r="A172" s="10" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B172" s="10"/>
       <c r="C172" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D172" s="10">
         <v>14246</v>
@@ -12371,7 +12302,7 @@
         <v>40</v>
       </c>
       <c r="P172" s="10" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="Q172" s="10"/>
       <c r="R172" s="10"/>
@@ -12379,11 +12310,11 @@
     </row>
     <row r="173">
       <c r="A173" s="10" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B173" s="10"/>
       <c r="C173" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D173" s="10">
         <v>14246</v>
@@ -12422,7 +12353,7 @@
         <v>40</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -12430,11 +12361,11 @@
     </row>
     <row r="174">
       <c r="A174" s="10" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B174" s="10"/>
       <c r="C174" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D174" s="10">
         <v>14246</v>
@@ -12473,7 +12404,7 @@
         <v>40</v>
       </c>
       <c r="P174" s="10" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="Q174" s="10"/>
       <c r="R174" s="10"/>
@@ -12481,11 +12412,11 @@
     </row>
     <row r="175">
       <c r="A175" s="10" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B175" s="10"/>
       <c r="C175" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D175" s="10">
         <v>14246</v>
@@ -12524,7 +12455,7 @@
         <v>40</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -12532,11 +12463,11 @@
     </row>
     <row r="176">
       <c r="A176" s="10" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B176" s="10"/>
       <c r="C176" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D176" s="10">
         <v>14246</v>
@@ -12575,7 +12506,7 @@
         <v>40</v>
       </c>
       <c r="P176" s="10" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="Q176" s="10"/>
       <c r="R176" s="10"/>
@@ -12583,11 +12514,11 @@
     </row>
     <row r="177">
       <c r="A177" s="10" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B177" s="10"/>
       <c r="C177" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D177" s="10">
         <v>14246</v>
@@ -12626,7 +12557,7 @@
         <v>40</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -12634,11 +12565,11 @@
     </row>
     <row r="178">
       <c r="A178" s="10" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B178" s="10"/>
       <c r="C178" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D178" s="10">
         <v>14246</v>
@@ -12671,13 +12602,13 @@
         <v>0</v>
       </c>
       <c r="N178" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O178" s="10" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="P178" s="10" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="Q178" s="10"/>
       <c r="R178" s="10"/>
@@ -12685,11 +12616,11 @@
     </row>
     <row r="179">
       <c r="A179" s="10" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B179" s="10"/>
       <c r="C179" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D179" s="10">
         <v>14246</v>
@@ -12722,13 +12653,13 @@
         <v>0</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O179" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="P179" s="10" t="s">
         <v>360</v>
-      </c>
-      <c r="P179" s="10" t="s">
-        <v>363</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -12736,11 +12667,11 @@
     </row>
     <row r="180">
       <c r="A180" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B180" s="10"/>
       <c r="C180" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D180" s="10">
         <v>14246</v>
@@ -12773,13 +12704,13 @@
         <v>0</v>
       </c>
       <c r="N180" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O180" s="10" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="P180" s="10" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="Q180" s="10"/>
       <c r="R180" s="10"/>
@@ -12787,11 +12718,11 @@
     </row>
     <row r="181">
       <c r="A181" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B181" s="10"/>
       <c r="C181" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D181" s="10">
         <v>14246</v>
@@ -12824,13 +12755,13 @@
         <v>0</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O181" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="P181" s="10" t="s">
         <v>360</v>
-      </c>
-      <c r="P181" s="10" t="s">
-        <v>363</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>

--- a/Data Sheets/Entities.xlsx
+++ b/Data Sheets/Entities.xlsx
@@ -753,7 +753,7 @@
     <t>43U</t>
   </si>
   <si>
-    <t>Calibre = 20, Range = 3000, ReloadTime = 4.5, MagazineSize = 120, HorizontalRecoil = 1, MinVerticalRecoil = -0.3, MaxVerticalRecoil = 0.7, SeriesTimeOffset = 0.1, RecoilDuration = 0.3, RecoilRecovery = 0.2, RecoilGrowthRate = 0.07, RecoilRecoveryRate = 0.99, SkippedShells = 3</t>
+    <t>Calibre = 20, Range = 5000, ReloadTime = 0.1, MagazineSize = 120, HorizontalRecoil = 1, MinVerticalRecoil = -0.3, MaxVerticalRecoil = 0.7, SeriesTimeOffset = 0.1, RecoilDuration = 0.3, RecoilRecovery = 0.2, RecoilGrowthRate = 0.07, RecoilRecoveryRate = 0.99, SkippedShells = 3</t>
   </si>
   <si>
     <t>Generic Gun - 2.0 cm</t>

--- a/Data Sheets/Entities.xlsx
+++ b/Data Sheets/Entities.xlsx
@@ -666,7 +666,7 @@
     <t>Artillery - 8.8 cm</t>
   </si>
   <si>
-    <t>Calibre = 88, Range = 12000, ReloadTime = 0.1, MagazineSize = 4, HorizontalRecoil = 0.0, MinVerticalRecoil = 0.0, MaxVerticalRecoil = 0.0, SeriesTimeOffset = 0, RecoilDuration = 0.23, RecoilRecovery = 0.2, RecoilGrowthRate = 1.0, RecoilRecoveryRate = 0.996</t>
+    <t>Calibre = 88, Range = 12000, ReloadTime = 0.1, MagazineSize = 1, HorizontalRecoil = 0.0, MinVerticalRecoil = 0.0, MaxVerticalRecoil = 0.0, SeriesTimeOffset = 0, RecoilDuration = 0.23, RecoilRecovery = 0.2, RecoilGrowthRate = 1.0, RecoilRecoveryRate = 0.996</t>
   </si>
   <si>
     <t>Gyrocompass</t>
@@ -753,7 +753,7 @@
     <t>43U</t>
   </si>
   <si>
-    <t>Calibre = 20, Range = 5000, ReloadTime = 0.1, MagazineSize = 120, HorizontalRecoil = 1, MinVerticalRecoil = -0.3, MaxVerticalRecoil = 0.7, SeriesTimeOffset = 0.1, RecoilDuration = 0.3, RecoilRecovery = 0.2, RecoilGrowthRate = 0.07, RecoilRecoveryRate = 0.99, SkippedShells = 3</t>
+    <t>Calibre = 20, Range = 5000, ReloadTime = 0.1, MagazineSize = 120, HorizontalRecoil = 1, MinVerticalRecoil = -0.3, MaxVerticalRecoil = 0.7, SeriesTimeOffset = 0.1, RecoilDuration = 0.3, RecoilRecovery = 0.2, RecoilGrowthRate = 0.07, RecoilRecoveryRate = 0.99, SkippedShells = 1</t>
   </si>
   <si>
     <t>Generic Gun - 2.0 cm</t>
